--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132968355</v>
       </c>
       <c r="B2" t="n">
-        <v>96712</v>
+        <v>96715</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132968355</v>
       </c>
       <c r="B2" t="n">
-        <v>96715</v>
+        <v>96716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132968355</v>
       </c>
       <c r="B2" t="n">
-        <v>96716</v>
+        <v>96718</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>133651736</v>
       </c>
       <c r="B3" t="n">
-        <v>96769</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132968355</v>
+        <v>133373320</v>
       </c>
       <c r="B2" t="n">
-        <v>96728</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Graversfors, Ög</t>
+          <t>Söder om Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567324</v>
+        <v>567236</v>
       </c>
       <c r="R2" t="n">
-        <v>6506384</v>
+        <v>6506426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +764,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Andreas Mathisen, Hasse Andersson, Lena Lundin Johansson, Rebecca Wikström, Simon Wikström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133651736</v>
+        <v>132968355</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,20 +804,32 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Granstorp, Norra Granstorp, Ög</t>
+          <t>Graversfors, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567365</v>
+        <v>567324</v>
       </c>
       <c r="R3" t="n">
-        <v>6506493</v>
+        <v>6506384</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,28 +867,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Emma Nordenberg, Andreas Mathisen, Hasse Andersson, Lena Lundin Johansson, Rebecca Wikström, Simon Wikström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134270668</v>
+        <v>133651736</v>
       </c>
       <c r="B4" t="n">
-        <v>58349</v>
+        <v>96783</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,45 +897,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söder om Norra Granstorp, Ög</t>
+          <t>Norra Granstorp, Norra Granstorp, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567264</v>
+        <v>567365</v>
       </c>
       <c r="R4" t="n">
-        <v>6506438</v>
+        <v>6506493</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,15 +981,120 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134270668</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58349</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söder om Norra Granstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567264</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6506438</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19806-2026 artfynd.xlsx
+++ b/artfynd/A 19806-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133373320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132968355</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133651736</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,8 +1115,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134270668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>